--- a/Result/21-12-24/NASDAQstock_21-12-24period252RS90.xlsx
+++ b/Result/21-12-24/NASDAQstock_21-12-24period252RS90.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/21-12-24/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE66D48-D9C7-E648-B122-2FD394B45E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F48D601-91E3-0440-B11A-FFD7EA99D671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -658,12 +658,14 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
+      <family val="1"/>
       <charset val="136"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="新細明體"/>
+      <family val="1"/>
       <charset val="136"/>
     </font>
     <font>

--- a/Result/21-12-24/NASDAQstock_21-12-24period252RS90.xlsx
+++ b/Result/21-12-24/NASDAQstock_21-12-24period252RS90.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/21-12-24/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F48D601-91E3-0440-B11A-FFD7EA99D671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9CADBC-DECD-6048-AC2B-D7087DE30275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
